--- a/Result/profitability/7828.xlsx
+++ b/Result/profitability/7828.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM9"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,7 +1118,7 @@
         <v>-16</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1147,10 +1147,10 @@
         <v>114.2</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.91</v>
+        <v>-0.9</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.978260869565217</v>
+        <v>-1.956521739130435</v>
       </c>
       <c r="Y6" t="n">
         <v>10.21000000000001</v>
@@ -1159,10 +1159,10 @@
         <v>0.1652103559870552</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
       <c r="AB6" t="n">
-        <v>8</v>
+        <v>7.799999999999999</v>
       </c>
       <c r="AC6" t="n">
         <v>-2.809999999999988</v>
@@ -1270,10 +1270,10 @@
         <v>114.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.044444444444444</v>
+        <v>-4.113636363636363</v>
       </c>
       <c r="Y7" t="n">
         <v>7.399999999999991</v>
@@ -1490,7 +1490,7 @@
         <v>1.02</v>
       </c>
       <c r="M9" t="n">
-        <v>1.57375</v>
+        <v>1.575</v>
       </c>
       <c r="N9" t="n">
         <v>52.9025</v>
@@ -1571,6 +1571,133 @@
       </c>
       <c r="AM9" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7828</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>359</v>
+      </c>
+      <c r="D10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E10" t="n">
+        <v>284</v>
+      </c>
+      <c r="F10" t="n">
+        <v>79.13</v>
+      </c>
+      <c r="G10" t="n">
+        <v>163</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>45.36%</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>171</v>
+      </c>
+      <c r="K10" t="n">
+        <v>135</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.0075</v>
+      </c>
+      <c r="N10" t="n">
+        <v>53.44125</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.343137254901961</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1.050000000000011</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.01309553504614636</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.11999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.09887515622830145</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
